--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_280_R28.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_280_R28.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.2263</v>
+        <v>9.389799999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>10.3748</v>
+        <v>8.605499999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8516</v>
+        <v>0.7844</v>
       </c>
       <c r="G2" t="n">
         <v>1.3655</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>3.018</v>
+        <v>1.1815</v>
       </c>
       <c r="T2" t="n">
-        <v>2.5558</v>
+        <v>0.7866</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4621</v>
+        <v>0.3949</v>
       </c>
       <c r="V2" t="n">
         <v>5.2192</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.7387</v>
+        <v>6.2435</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2233</v>
+        <v>5.4592</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5154</v>
+        <v>0.7843</v>
       </c>
       <c r="G3" t="n">
         <v>4.925</v>
@@ -688,13 +688,13 @@
         <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0457</v>
+        <v>0.5504</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0474</v>
+        <v>0.2833</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0018</v>
+        <v>0.2671</v>
       </c>
       <c r="V3" t="n">
         <v>0.5361</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3994</v>
+        <v>4.5338</v>
       </c>
       <c r="E4" t="n">
         <v>4.032</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3674</v>
+        <v>0.5018</v>
       </c>
       <c r="G4" t="n">
         <v>2.1241</v>
@@ -766,13 +766,13 @@
         <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0975</v>
+        <v>0.232</v>
       </c>
       <c r="T4" t="n">
         <v>0.4208</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3233</v>
+        <v>-0.1889</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1418</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.207</v>
+        <v>-0.3085</v>
       </c>
       <c r="E5" t="n">
-        <v>0.395</v>
+        <v>0.1591</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6021</v>
+        <v>-0.4676</v>
       </c>
       <c r="G5" t="n">
         <v>-1.2353</v>
@@ -844,13 +844,13 @@
         <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0439</v>
+        <v>-0.1454</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3383</v>
+        <v>0.1024</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3822</v>
+        <v>-0.2478</v>
       </c>
       <c r="V5" t="n">
         <v>1.0722</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.828</v>
+        <v>-0.6584</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9242</v>
+        <v>0.1316</v>
       </c>
       <c r="F6" t="n">
-        <v>0.09619999999999999</v>
+        <v>-0.79</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1043</v>
+        <v>-0.7744</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.468</v>
+        <v>-0.4632</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.6363</v>
+        <v>-0.3111</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.121</v>
+        <v>0.1944</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0133</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1077</v>
+        <v>0.1104</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9833</v>
+        <v>-0.9688</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4547</v>
+        <v>-0.5473</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5286</v>
+        <v>-0.4216</v>
       </c>
       <c r="P6" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7248</v>
+        <v>-0.5799</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1968</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.528</v>
+        <v>-0.5171</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9615</v>
+        <v>-0.8572</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1043</v>
+        <v>-0.5747</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8572</v>
+        <v>-0.2825</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7744</v>
+        <v>-2.9523</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4632</v>
+        <v>-0.1719</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3111</v>
+        <v>-2.7805</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1944</v>
+        <v>-0.225</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08400000000000001</v>
+        <v>1.2372</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1104</v>
+        <v>-1.4623</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9688</v>
+        <v>-2.7273</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5473</v>
+        <v>-1.4091</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4216</v>
+        <v>-1.3182</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.883</v>
+        <v>0.1494</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2987</v>
+        <v>-0.3497</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5843</v>
+        <v>0.4991</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0736</v>
+        <v>-0.9386</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7359</v>
+        <v>-0.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3378</v>
+        <v>-0.4386</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3902</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0751</v>
+        <v>0.06</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U8" t="n">
-        <v>0.597</v>
+        <v>0.4962</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5361</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1946</v>
+        <v>-0.9789</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0465</v>
+        <v>-0.8062</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.148</v>
+        <v>-0.1726</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9523</v>
+        <v>-2.1043</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1719</v>
+        <v>-0.468</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.7805</v>
+        <v>-1.6363</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.225</v>
+        <v>-1.121</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2372</v>
+        <v>-0.0133</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.4623</v>
+        <v>-1.1077</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.7273</v>
+        <v>-0.9833</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4091</v>
+        <v>-0.4547</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3182</v>
+        <v>-0.5286</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.188</v>
+        <v>0.5739</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8215</v>
+        <v>0.3148</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6335</v>
+        <v>0.2592</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.7045</v>
+        <v>-1.4178</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1937</v>
+        <v>-1.8398</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4892</v>
+        <v>0.422</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5616</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4112</v>
+        <v>0.6978</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1221</v>
+        <v>0.476</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2891</v>
+        <v>0.2219</v>
       </c>
       <c r="V10" t="n">
         <v>0.6778999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5556</v>
+        <v>-3.1682</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7602</v>
+        <v>-2.4063</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7954</v>
+        <v>-0.7618</v>
       </c>
       <c r="G11" t="n">
         <v>-1.6478</v>
@@ -1312,13 +1312,13 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7481</v>
+        <v>-0.3607</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7468</v>
+        <v>-0.393</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0013</v>
+        <v>0.0323</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.8396</v>
+        <v>11.8395</v>
       </c>
       <c r="E12" t="n">
-        <v>12.2603</v>
+        <v>12.2604</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4206999999999998</v>
+        <v>-0.4206</v>
       </c>
       <c r="G12" t="n">
         <v>-4.2513</v>
@@ -1375,7 +1375,7 @@
         <v>-18.6961</v>
       </c>
       <c r="N12" t="n">
-        <v>-9.997400000000001</v>
+        <v>-9.997399999999999</v>
       </c>
       <c r="O12" t="n">
         <v>-8.6989</v>
@@ -1390,16 +1390,16 @@
         <v>18.5563</v>
       </c>
       <c r="S12" t="n">
-        <v>2.3591</v>
+        <v>2.359</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1421</v>
+        <v>1.1422</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2168</v>
+        <v>1.2169</v>
       </c>
       <c r="V12" t="n">
-        <v>5.613499999999999</v>
+        <v>5.6135</v>
       </c>
       <c r="W12" t="n">
         <v>7.111100000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.297</v>
+        <v>2.1848</v>
       </c>
       <c r="E13" t="n">
-        <v>4.4261</v>
+        <v>4.1902</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.129</v>
+        <v>-2.0054</v>
       </c>
       <c r="G13" t="n">
         <v>3.3351</v>
@@ -1468,13 +1468,13 @@
         <v>1.3917</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3369</v>
+        <v>-0.4492</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3339</v>
+        <v>-0.5698</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0031</v>
+        <v>0.1206</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8608</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>A. BLAKENEY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2344</v>
+        <v>0.9428</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3389</v>
+        <v>3.1257</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.1045</v>
+        <v>-2.183</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8988</v>
+        <v>-0.38</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1154</v>
+        <v>1.8149</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0142</v>
+        <v>-2.195</v>
       </c>
       <c r="J14" t="n">
-        <v>3.7655</v>
+        <v>2.1792</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6944</v>
+        <v>3.2132</v>
       </c>
       <c r="L14" t="n">
-        <v>2.071</v>
+        <v>-1.0341</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8666</v>
+        <v>-2.5592</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8099</v>
+        <v>-1.3983</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0568</v>
+        <v>-1.1609</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.0876</v>
+        <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7842</v>
+        <v>-0.2133</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1766</v>
+        <v>-0.1256</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9608</v>
+        <v>-0.0876</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="W14" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BLAKENEY</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2129</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6539</v>
+        <v>2.221</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.4411</v>
+        <v>-1.6086</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.38</v>
+        <v>1.8988</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8149</v>
+        <v>-0.1154</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.195</v>
+        <v>2.0142</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1792</v>
+        <v>3.7655</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2132</v>
+        <v>1.6944</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.0341</v>
+        <v>2.071</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5592</v>
+        <v>-1.8666</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3983</v>
+        <v>-1.8099</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1609</v>
+        <v>-0.0568</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-1.3917</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9432</v>
+        <v>0.1621</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5975</v>
+        <v>-0.2946</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3457</v>
+        <v>0.4567</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>-2.1444</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>V. MICIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6691</v>
+        <v>-0.9808</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1222</v>
+        <v>-2.1547</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7913</v>
+        <v>1.1739</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2206</v>
+        <v>5.1472</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.4323</v>
+        <v>0.4563</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2117</v>
+        <v>4.6909</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1598</v>
+        <v>5.9201</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2128</v>
+        <v>1.7512</v>
       </c>
       <c r="L16" t="n">
-        <v>3.3726</v>
+        <v>4.1689</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3804</v>
+        <v>-0.7729</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2195</v>
+        <v>-1.2949</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1609</v>
+        <v>0.5221</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6237</v>
+        <v>-5.3349</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3195</v>
+        <v>-7.1905</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1751</v>
+        <v>-0.7932</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2819</v>
+        <v>-0.8843</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1067</v>
+        <v>0.0912</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7916</v>
+        <v>-1.2298</v>
       </c>
       <c r="E17" t="n">
-        <v>0.637</v>
+        <v>0.1652</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4286</v>
+        <v>-1.395</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3788</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.6594</v>
+        <v>0.2212</v>
       </c>
       <c r="T17" t="n">
-        <v>0.637</v>
+        <v>0.1652</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>V. MICIC</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5192</v>
+        <v>-1.3729</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.3906</v>
+        <v>-2.312</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8714</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>5.1472</v>
+        <v>-1.9902</v>
       </c>
       <c r="H18" t="n">
-        <v>0.4563</v>
+        <v>-2.8099</v>
       </c>
       <c r="I18" t="n">
-        <v>4.6909</v>
+        <v>0.8198</v>
       </c>
       <c r="J18" t="n">
-        <v>5.9201</v>
+        <v>-1.4277</v>
       </c>
       <c r="K18" t="n">
-        <v>1.7512</v>
+        <v>-0.5175</v>
       </c>
       <c r="L18" t="n">
-        <v>4.1689</v>
+        <v>-0.9102</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7729</v>
+        <v>-0.5625</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2949</v>
+        <v>-2.2925</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5221</v>
+        <v>1.73</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.3349</v>
+        <v>1.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-7.1905</v>
+        <v>-0.232</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3315</v>
+        <v>-0.7745</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1202</v>
+        <v>-0.6524</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2113</v>
+        <v>-0.1221</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.035</v>
+        <v>-1.4776</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5479</v>
+        <v>0.4145</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5129</v>
+        <v>-1.8921</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.9902</v>
+        <v>-0.2206</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.8099</v>
+        <v>-2.4323</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8198</v>
+        <v>2.2117</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.4277</v>
+        <v>2.1598</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5175</v>
+        <v>-1.2128</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.9102</v>
+        <v>3.3726</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5625</v>
+        <v>-2.3804</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.2925</v>
+        <v>-1.2195</v>
       </c>
       <c r="O19" t="n">
-        <v>1.73</v>
+        <v>-1.1609</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3917</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4365</v>
+        <v>0.3666</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8883</v>
+        <v>0.5742</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5482</v>
+        <v>-0.2076</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y. MADAR</t>
+          <t>T. ODIASE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2731</v>
+        <v>-2.0051</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4043</v>
+        <v>-1.4711</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8689</v>
+        <v>-0.534</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9785</v>
+        <v>-0.2822</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9351</v>
+        <v>0.0457</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0435</v>
+        <v>-0.3279</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6729000000000001</v>
+        <v>0.7186</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.5714</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5889</v>
+        <v>0.1472</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6514</v>
+        <v>-1.0008</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0191</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6323</v>
+        <v>-0.4751</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.9278</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3668</v>
+        <v>0.1327</v>
       </c>
       <c r="T20" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.1298</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4494</v>
+        <v>0.0029</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. ODIASE</t>
+          <t>Y. MADAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3254</v>
+        <v>-2.1216</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.825</v>
+        <v>-0.2863</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5004</v>
+        <v>-1.8353</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2822</v>
+        <v>-0.9785</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0457</v>
+        <v>-0.9351</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3279</v>
+        <v>-0.0435</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7186</v>
+        <v>0.6729000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5714</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1472</v>
+        <v>0.5889</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0008</v>
+        <v>-1.6514</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-1.0191</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4751</v>
+        <v>-0.6323</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.8556</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1876</v>
+        <v>-0.2153</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.224</v>
+        <v>0.2005</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0365</v>
+        <v>-0.4158</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.4892</v>
+        <v>-2.7359</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5137</v>
+        <v>-1.7496</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9755</v>
+        <v>-0.9863</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6705</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0215</v>
+        <v>-0.2251</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2715</v>
+        <v>0.0356</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.25</v>
+        <v>-0.2607</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4813</v>
+        <v>-2.8694</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.076</v>
+        <v>-1.7221</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4054</v>
+        <v>-1.1473</v>
       </c>
       <c r="G23" t="n">
         <v>-0.229</v>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3967</v>
+        <v>0.2153</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1494</v>
+        <v>0.2045</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2473</v>
+        <v>0.0108</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,31 +2281,31 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-11.8396</v>
+        <v>-11.0531</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4205999999999999</v>
+        <v>0.420800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-12.2604</v>
+        <v>-11.4741</v>
       </c>
       <c r="G24" t="n">
-        <v>4.2513</v>
+        <v>4.251299999999998</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.147200000000001</v>
+        <v>-4.147199999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>8.3985</v>
+        <v>8.398499999999999</v>
       </c>
       <c r="J24" t="n">
         <v>18.6962</v>
       </c>
       <c r="K24" t="n">
-        <v>9.997200000000001</v>
+        <v>9.997199999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>8.698700000000001</v>
+        <v>8.698700000000002</v>
       </c>
       <c r="M24" t="n">
         <v>-14.4449</v>
@@ -2314,7 +2314,7 @@
         <v>-14.1447</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2999999999999998</v>
+        <v>-0.3</v>
       </c>
       <c r="P24" t="n">
         <v>-8.1182</v>
@@ -2326,13 +2326,13 @@
         <v>10.438</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.359</v>
+        <v>-1.5727</v>
       </c>
       <c r="T24" t="n">
         <v>-1.2169</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.142</v>
+        <v>-0.3555999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-5.613500000000001</v>
